--- a/docs/Reports & Plans/GV-LSO-Analysis.xlsx
+++ b/docs/Reports & Plans/GV-LSO-Analysis.xlsx
@@ -571,7 +571,7 @@
     <row r="7" ht="110" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>A REVERSE-KNIGHT: instead of 5-6 big models, ~50-60 elite bodies that are hard to kill and hard to move. The win-con is CONVERGENCE, not raw guns: Oath of Moment names ONE enemy unit/turn and the whole army re-rolls Hits + adds +1 to Wound into it — roughly DOUBLING every unit's output onto that target. Wrapped around an un-shockable OC22 Terminator brick (Lysander) that one-rounds anything in melee, an unsaveable Sternguard Dev-Wound chipper, AP-2 cyclone missiles, and mobile Land Speeder melta. Defence: 2+/4++ + Armour of Contempt (-1 AP army-wide) + sticky objectives + hidden deploy. It rarely gets tabled and rarely gets out-scored — it grinds you down and holds what it takes.</t>
+          <t>A REVERSE-KNIGHT: instead of 5-6 big models, ~50-60 elite bodies that are hard to kill and hard to move. The win-con is CONVERGENCE, not raw guns: Oath of Moment names ONE enemy unit/turn and the whole army re-rolls Hits + adds +1 to Wound into it — roughly DOUBLING every unit's output onto that target. Wrapped around an un-shockable OC22 Terminator brick (Lysander) that one-rounds anything in melee, an unsaveable Sternguard Dev-Wound chipper, AP-2 cyclone missiles, and mobile Land Speeder melta. Defence: 2+/4++ (the real workhorse) + sticky objectives + hidden deploy. It rarely gets tabled and rarely gets out-scored — it grinds you down and holds what it takes. NOTE: Armour of Contempt is NOT army-wide durability — it's a 1-CP Strat that blunts ONE attacker's AP-by-1 on ONE unit, once per phase, and only helps vs AP-1/-2 (nothing vs high-AP/invuln/Dev). With only ~1 CP/turn it's an occasional, well-timed tool, not a passive.</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>+ Librarian [Temporal Corridor]. The UNSAVEABLE chipper: Sternguard bolt rifle S4 AP-1 D1 [Dev, RF1] + FULL wound-reroll vs Oath -&gt; ~5-7 mortal wounds/turn skipping any invuln. Character/W1 sniper.</t>
+          <t>+ Librarian [Temporal Corridor]. The UNSAVEABLE chipper: Sternguard bolt rifle S4 AP-1 D1 [Dev, RF1] + FULL wound-reroll vs Oath -&gt; ~5-7 mortal wounds/turn skipping any invuln. It CLEARS W1/W2 UNITS wholesale — but has NO Precision, so it can't snipe an attached Character; that's Lysander + Epic Challenge in melee.</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1005,16 +1005,16 @@
           <t>High (5)</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>FAVOURABLE (survive round 1)</t>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>COIN-FLIP -&gt; favourable (the alpha is REAL)</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>A glass alpha vs your armour: Armour of Contempt drops their AP, the 4++ eats the Dev-rail/fusion spikes, and your reserves mean the alpha has less to hit turn 1. Oath one-rounds Crisis/Riptides; the brick walks them down.
-PLAN: • Reserve heavy; give the T'au alpha few juicy turn-1 targets. Armour of Contempt on the unit they focus.  • Oath the Retaliation Crisis bomb the turn it drops (before Fire-and-Fade) — Sternguard Dev + brick delete it.  • Grind forward; T'au can't out-durable or out-melee you. Kill the markerlight Pathfinders to cut their hit-buffs.
-WATCH: A perfectly-piloted markerlit railgun turn can chunk the brick — spread the Termies, don't clump for Blast.</t>
+          <t>Their anti-elite is Railgun AP-5 / heavy rail AP-4 / fusion AP-4 — NO AP-1, so ARMOUR OF CONTEMPT DOES NOTHING here (AP that high already negates armour; an invuln is never modified by AP). You're on the 4++ ALONE (fails half), and the railgun/rail DEVASTATING WOUNDS turn crits into MORTALS that bypass the 4++ too — a markerlit alpha CAN delete the brick. Your edge isn't your saves, it's RESERVES (few T1 targets) + T'au fragility: Oath one-rounds Crisis/Riptides and the brick walks down anything that lingers. Survive the alpha, then out-grind.
+PLAN: • Reserve heavy + hide the brick from first-turn rail/fusion LoS — the alpha can't hurt what it can't see. (Don't waste CP on Armour of Contempt vs their AP-4/-5; it does nothing.)  • In YOUR Command phase each turn, Oath the biggest suit unit ON THE BOARD (Sternguard Dev + cyclone + brick erase it). You commit PROACTIVELY — you CANNOT Oath a unit the turn it deep-strikes in (that's the opponent's turn).  • Grind forward; T'au can't out-durable or out-melee you. Kill markerlight Pathfinders to cut the hit-buffs; make them Fire-and-Fade off objectives.
+WATCH: Railgun/heavy rail are DEVASTATING WOUNDS -&gt; crit MORTALS bypass your 4++, and AP-4/-5 makes armour moot, so a markerlit rail turn chunks the brick. Keep Terminators spread to limit MORTAL-WOUND SPILLOVER — NOT for 'Blast' (the railgun isn't a Blast weapon, and Blast counts MODELS in the unit, not their spacing, so spreading doesn't reduce it).</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
         <is>
           <t>Mirror of elites: their 2+/4++ + better melee weapons vs your 2+/4++ + more bodies + Oath + unsaveable Sternguard. They out-fight the brick model-for-model; you out-number and out-shoot (Dev bypasses their 4++).
 PLAN: • Do NOT brawl the Blade Champion/Wardens with the brick head-on — Oath + Sternguard Dev SHOOT them down (mortals skip the 4++).  • Use your body count + sticky OC to out-score; they have ~40 models, you have more.  • Speeders melta the Caladius; cyclone + Oath delete a Custodian unit/turn.
-WATCH: Their characters (Trajann/Blade Champion) out-duel Lysander — snipe with Sternguard, don't melee.</t>
+WATCH: Trajann/Blade Champion out-duel Lysander AND are ATTACHED (you can't snipe them) — grind the whole unit down with Oath volume, or use EPIC CHALLENGE (1CP) to give Lysander's Fist [PRECISION] and kill the character in melee. Don't feed Lysander in unbuffed.</t>
         </is>
       </c>
     </row>
@@ -1100,8 +1100,8 @@
       <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Glass melee alpha into your armour: Death Company/Sang Guard hit hard on the charge but fold to return fire, and Armour of Contempt + 4++ blunts their AP. Oath + overwatch thin the alpha as it lands; the brick counter-punches.
-PLAN: • Screen so the DC/Sang Guard land 9"+ out; Oath the deepest-striking unit and delete it before it swings.  • Weather the charge behind 2+/4++/AoC; the brick one-rounds Dante/Sanguinary Guard back.  • Out-grind — they're fragile once the alpha is spent.
-WATCH: Lemartes/Priests keeping DC alive — Oath+Sternguard the character to strip the buffs.</t>
+PLAN: • Screen so the DC/Sang Guard land 9"+ out and can't reach a T2 charge (overwatch thins them). Then on YOUR turn Oath the landed unit and gun it down — you can't Oath it as it arrives in their turn.  • Weather the charge behind 2+/4++/AoC; the brick one-rounds Dante/Sanguinary Guard back.  • Out-grind — they're fragile once the alpha is spent.
+WATCH: Lemartes/Priests are ATTACHED to the DC/Sang-Guard (you CANNOT target them) — grind the whole unit down with Oath volume, or Lysander + EPIC CHALLENGE (1CP -&gt; [PRECISION]) to assassinate the buff-char in melee.</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
         <is>
           <t>Terminator mirror: their Deathwing Knights (4++, mace, Smite of the Watchers) + Lion vs your Lysander brick + Sternguard. Both durable; comes down to Oath efficiency + who out-scores. The Lion out-duels Lysander in melee.
 PLAN: • SHOOT the Deathwing down with Oath + Sternguard Dev (mortals skip the 4++) — don't melee the mace brick.  • Race objectives; both armies are slow, so board position + sticky OC decide it.  • Speeders + cyclone delete the Ravenwing speeders / support first.
-WATCH: The Lion — do not feed Lysander into him; Sternguard-snipe or avoid.</t>
+WATCH: The Lion is a STANDALONE Monster (directly targetable) — Oath + shoot him down at range (no Precision needed). Do NOT feed Lysander into him in melee.</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
         <is>
           <t>Their lascannon/volcano over-kills your W2-3 bodies (D6 into W2 = waste), and their infantry can't out-fight yours. You advance behind AoC, Oath the superheavies (or ignore and out-score), and the brick/Speeders crack the tanks.
 PLAN: • Reserve vs the alpha; advance into the gunline (they're static). Oath the Shadowsword/Baneblade or just out-score around it.  • Speeder melta + brick delete a superheavy if it's the win-con; otherwise take objectives their tanks can't hold.  • Sticky OC + body count out-scores a low-model Guard tank list.
-WATCH: Artillery + Leontus orders can chip; don't clump for the big blasts.</t>
+WATCH: Artillery + Leontus orders can chip. Spread bodies to limit mortal/spillover from the big guns — but note spreading does NOT reduce a [BLAST] weapon's shots (Blast = +1 attack per 5 models IN the target unit, regardless of spacing); to cut Blast you bring smaller units.</t>
         </is>
       </c>
     </row>
@@ -1350,9 +1350,9 @@
       <c r="B7" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>FAV</t>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>COIN</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
@@ -1546,7 +1546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>-1 AP to incoming attacks army-wide (stratagem). Drops enemy AP-2 -&gt; AP-1; makes the 2+/4++ bodies brutally durable.</t>
+          <t>-1 AP to incoming attacks (stratagem). Drops enemy AP-2 -&gt; AP-1; brutal vs AP-1/-2 VOLUME (the common case). BUT does NOTHING vs AP-4/-5 (armour already negated) or whenever you're taking an INVULN save (AP never modifies an invuln), and NOTHING vs Devastating/mortal wounds -- so it does not save you from railguns/fusion/Dev spikes.</t>
         </is>
       </c>
     </row>
@@ -1680,29 +1680,53 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Killing characters (NO Precision)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Sternguard/cyclone/brick have NO [PRECISION] -&gt; you canNOT snipe a Character attached to a Bodyguard unit (wounds hit the bodyguard). Tools: (1) grind the whole unit down with Oath volume, exposing the char; (2) EPIC CHALLENGE (core strat 15.03, 1CP) -&gt; Lysander's Fist gains [PRECISION] to assassinate an ATTACHED char in MELEE; (3) STANDALONE Monster/Titanic chars (Fulgrim/Magnus/Lion/superheavy) = shoot DIRECTLY. Oath the UNIT, not the character.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>CP economy (~2/round)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1 CP at the start of EACH player-turn (~10/game) + CP-model/discard extras. Oath of Moment is FREE (army rule). BUT Armour of Contempt, Fury of the First, Disciplined Extermination, Dropship Extraction, Wrathful Conquerors AND Epic Challenge all COMPETE for ~1 strat/turn -&gt; you cannot fire them all. Each turn pick ONE priority: the offence convergence strat, OR defensive AoC, OR Epic Challenge -- and hold CP for the swing turns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>MINDSET</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>GV is 'always outnumbered by big things, never out-graunched by small ones.' You are the DURABLE, STICKY, all-comers list — you rarely get tabled and rarely get out-scored. Play the OATH like a sniper (one perfect target/turn), weather the enemy's alpha behind 2+/4++ + Armour of Contempt, and win the LONG GAME on sticky objectives + attrition. Your two failure modes: (1) getting out-BODIED/out-OC'd by a true horde, and (2) getting out-MANOEUVRED and out-scored by a faster army while your M5 bricks are stranded. Deploy your homers to control WHERE the alpha lands; never waste the Oath on a target you can't finish.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>GV is 'always outnumbered by big things, never out-graunched by small ones.' You are the DURABLE, STICKY, all-comers list — you rarely get tabled and rarely get out-scored. Play the OATH like a sniper (one perfect target/turn), weather the enemy's alpha behind 2+/4++ (Armour of Contempt helps only vs AP-1/-2 volume, NOT railguns/fusion/Dev), and win the LONG GAME on sticky objectives + attrition. Your two failure modes: (1) getting out-BODIED/out-OC'd by a true horde, and (2) getting out-MANOEUVRED and out-scored by a faster army while your M5 bricks are stranded. Deploy your homers to control WHERE the alpha lands; never waste the Oath on a target you can't finish.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>RECORD</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="150" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="19" ht="150" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Great Value is a STRONG all-comers list — a better raw record expectation than a Knight army because it has FEWER hard counters. Realistic 300+ GT: a solidly positive record, ~4-2 to 5-1 over 5-6 rounds, with a genuine shot at the top tables. It wins by DURABILITY + CONVERGENCE + STICKY OBJECTIVES, not by any single alpha. The two things that beat it: a true HORDE that out-bodies the OC (Orks) and a fast army that out-manoeuvres the M5 bricks and out-scores while refusing the fight (kite-and-flip). Its own discipline test: pilot the Oath perfectly (one finishable target/turn) and don't strand the bricks. Blind spots: (1) M5 bricks are slow -&gt; board control depends on the mobile legs + homers, protect them; (2) psyker-dependent (Conclave) -&gt; Culexus/Callidus/character-snipes throttle it, screen the Librarians; (3) reserve-heavy -&gt; a whiffed turn-2 arrival (failed charges / scattered homers) is a lost tempo swing.</t>
         </is>
@@ -1711,10 +1735,10 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A19:B19"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Reports & Plans/GV-LSO-Analysis.xlsx
+++ b/docs/Reports & Plans/GV-LSO-Analysis.xlsx
@@ -571,7 +571,7 @@
     <row r="7" ht="110" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>A REVERSE-KNIGHT: instead of 5-6 big models, ~50-60 elite bodies that are hard to kill and hard to move. The win-con is CONVERGENCE, not raw guns: Oath of Moment names ONE enemy unit/turn and the whole army re-rolls Hits + adds +1 to Wound into it — roughly DOUBLING every unit's output onto that target. Wrapped around an un-shockable OC22 Terminator brick (Lysander) that one-rounds anything in melee, an unsaveable Sternguard Dev-Wound chipper, AP-2 cyclone missiles, and mobile Land Speeder melta. Defence: 2+/4++ (the real workhorse) + sticky objectives + hidden deploy. It rarely gets tabled and rarely gets out-scored — it grinds you down and holds what it takes. NOTE: Armour of Contempt is NOT army-wide durability — it's a 1-CP Strat that blunts ONE attacker's AP-by-1 on ONE unit, once per phase, and only helps vs AP-1/-2 (nothing vs high-AP/invuln/Dev). With only ~1 CP/turn it's an occasional, well-timed tool, not a passive.</t>
+          <t>A REVERSE-KNIGHT: instead of 5-6 big models, ~50-60 elite bodies that are hard to kill and hard to move. The win-con is CONVERGENCE, not raw guns: Oath of Moment names ONE enemy unit/turn and the whole army re-rolls Hits + adds +1 to Wound into it — roughly DOUBLING every unit's output onto that target. Wrapped around an OC22 Terminator brick (Lysander) that one-rounds anything in melee, an unsaveable Sternguard Dev-Wound chipper, AP-2 cyclone missiles, and mobile Land Speeder melta. Defence: 2+/4++ (the real workhorse) + sticky objectives + hidden deploy. It rarely gets tabled and rarely gets out-scored — it grinds you down and holds what it takes. NOTE: Armour of Contempt is NOT army-wide durability — it's a 1-CP Strat that blunts ONE attacker's AP-by-1 on ONE unit, once per phase, and only helps vs AP-1/-2 (nothing vs high-AP/invuln/Dev). With only ~1 CP/turn it's an occasional, well-timed tool, not a passive.</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>+ Darnath Lysander + Ancient in Terminator Armour = the OC22 BRICK. Thunder hammer S8 AP-2 D2 [Dev]; ~24-28 melee one-rounds ANY target. Un-shockable, M5, Teleport Homer.</t>
+          <t>+ Darnath Lysander + Ancient in Terminator Armour = the OC22 BRICK. Thunder hammer S8 AP-2 D2 [Dev]; ~24-28 melee one-rounds ANY target. M5, Teleport Homer. NOT battle-shock-immune (see below).</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Warlord. Inspiring Commander -&gt; non-Character Terminators become OC2 (brick = OC22, effectively permanent). Icon of Obstinacy (-1 to wound at S&gt;=5).</t>
+          <t>Warlord. Inspiring Commander -&gt; non-Character Terminators become OC2 (brick = OC22 while intact). Icon of Obstinacy (-1 to wound at S&gt;=5). Gives NO battle-shock immunity.</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -1043,7 +1043,7 @@
         <is>
           <t>C'tan durability (4++/-1Dmg/reanim) blunts even your convergence, and they out-OC with reanimating bodies. Your edge: Sternguard Dev MORTALS partly bypass reanimation, and the brick out-fights Wraiths. But you can't table 3 C'tan and they grind objectives.
 PLAN: • Oath + Sternguard Dev a C'tan each turn — mortals skip the 4++; you won't kill it but you suppress it.  • Don't feed the brick into the Void Dragon (Anti-Veh, heals off you); brick kills Wraiths/Lychguard instead.  • Win on sticky objectives + secondaries; it's a grind you can steal, not a matchup you dominate.
-WATCH: Reanimation refunding your chip — focus-remove whole units, don't spread.</t>
+WATCH: Reanimation refunding your chip — focus-remove whole units, don't spread. BATTLE-SHOCK: their 1CP C'tan strat forces the OC22 brick to test at -1 (+D3+1 mortals on fail) -&gt; a failed test zeroes its OC and shuts off its strats on the turn you most need it holding. Hold 1 CP for Insane Bravery when the brick is contesting a key objective.</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Non-Character Terminators in his unit become OC2 -&gt; the 10-brick is OC20 (+Lysander +Ancient = OC22). Battle-shock only tests below half strength (need 6+ dead first) -&gt; the OC22 is effectively PERMANENT and un-shockable.</t>
+          <t>Non-Character Terminators in his unit become OC2 -&gt; the 10-brick is OC20 (+Lysander +Ancient = OC22) WHILE INTACT. It won't take a Command-phase battle-shock test until below half strength (6+ dead), so vs most armies the OC22 holds. But Lysander grants NO battle-shock immunity: a FORCED test (see Battle-shock entry) can shock it at full strength -&gt; OC drops to '-' (0), so all that OC evaporates.</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Pick 1 Discipline/round; ALL psyker-led units (Sternguard + cyclone Termies) get it: Divination (rr-1s) / Pyromancy (+1 AP + Sustained) / Telekinesis (deep-strike enable, -1 S def) / etc.</t>
+          <t>Each round pick 1 Discipline; ALL friendly ADEPTUS ASTARTES PSYKER units get it until end of round (that's the Librarian-led Sternguard + the Librarian-in-Term cyclone brick — NOT the Lysander brick, it has no psyker). Verified from the pack: Biomancy = +2" M / Divination = re-roll Hit-1s AND Wound-1s / Pyromancy = +1 AP vs enemies within 12" / Telekinesis = -1 S to ranged attacks INTO the unit (defensive) / Telepathy = ignore BS/WS/hit-roll modifiers. Fusillade Enhancement makes the bearer's ranged attacks [LETHAL HITS], +[SUSTAINED HITS 1] if the unit also has Pyromancy. Typical pick: Pyromancy (turns the cyclone brick into +1 AP + Lethal + Sustained into the Oath target) or Divination for reliability.</t>
         </is>
       </c>
     </row>
@@ -1704,29 +1704,53 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Battle-shock — GV's HIDDEN weakness</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Core 01.07: a battle-shocked unit has OC '-' (0), CANNOT be targeted by ANY stratagem, and cannot do/finish Actions. GV's ENTIRE win-con is the OC22 brick out-scoring you on objectives -&gt; shock it and that collapses, AND you shut off his defensive strats on it (no AoC/Rotate-equivalent on a shocked unit). Lysander gives NO immunity. His mitigations: Insane Bravery (core 15.04, 1CP, auto-pass ONE test -&gt; competes for the same CP as everything else) and staying above half strength (no voluntary test). WEAPONIZERS to expect at LSO that FORCE tests at full strength: Tyranids (Shadow in the Warp = -1 Ld / forced tests near synapse), CSM (Dread Talons / Fear-based -1 &amp; forced), Necrons (forced-test tech), Chaos Daemons (terror/forced). Against those decks the OC22 is NOT reliable -- plan for it to drop to OC0 on a bad round.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Core strats cut BOTH ways</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Every army at LSO has the same 12 core stratagems (Section 15): Command Re-roll, Counter-offensive, Epic Challenge, Insane Bravery, Grenade, Tank Shock, Fire Overwatch, Smokescreen, Heroic Intervention, Rapid Ingress, Go to Ground, Armour of Contempt. So the OPPONENT can Epic-Challenge to snipe GV's characters in melee too, Counter-offensive to fight first, Rapid Ingress to steal the alpha, and Fire Overwatch the teleport drop. GV isn't the only one with these tricks -- budget CP for the enemy's core plays, not just your own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>MINDSET</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>GV is 'always outnumbered by big things, never out-graunched by small ones.' You are the DURABLE, STICKY, all-comers list — you rarely get tabled and rarely get out-scored. Play the OATH like a sniper (one perfect target/turn), weather the enemy's alpha behind 2+/4++ (Armour of Contempt helps only vs AP-1/-2 volume, NOT railguns/fusion/Dev), and win the LONG GAME on sticky objectives + attrition. Your two failure modes: (1) getting out-BODIED/out-OC'd by a true horde, and (2) getting out-MANOEUVRED and out-scored by a faster army while your M5 bricks are stranded. Deploy your homers to control WHERE the alpha lands; never waste the Oath on a target you can't finish.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>GV is 'always outnumbered by big things, never out-graunched by small ones.' You are the DURABLE, STICKY, all-comers list — you rarely get tabled and rarely get out-scored. Play the OATH like a sniper (one perfect target/turn), weather the enemy's alpha behind 2+/4++ (Armour of Contempt helps only vs AP-1/-2 volume, NOT railguns/fusion/Dev), and win the LONG GAME on sticky objectives + attrition. Your THREE failure modes: (1) getting out-BODIED/out-OC'd by a true horde, (2) getting out-MANOEUVRED and out-scored by a faster army while your M5 bricks are stranded, and (3) getting BATTLE-SHOCKED by a shock-weaponizer (Tyranids/CSM/Necrons/Daemons) -&gt; the OC22 brick drops to OC0 and its defensive strats switch off. Deploy your homers to control WHERE the alpha lands; hold 1 CP for Insane Bravery vs shock decks; never waste the Oath on a target you can't finish.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>RECORD</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="150" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="21" ht="150" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Great Value is a STRONG all-comers list — a better raw record expectation than a Knight army because it has FEWER hard counters. Realistic 300+ GT: a solidly positive record, ~4-2 to 5-1 over 5-6 rounds, with a genuine shot at the top tables. It wins by DURABILITY + CONVERGENCE + STICKY OBJECTIVES, not by any single alpha. The two things that beat it: a true HORDE that out-bodies the OC (Orks) and a fast army that out-manoeuvres the M5 bricks and out-scores while refusing the fight (kite-and-flip). Its own discipline test: pilot the Oath perfectly (one finishable target/turn) and don't strand the bricks. Blind spots: (1) M5 bricks are slow -&gt; board control depends on the mobile legs + homers, protect them; (2) psyker-dependent (Conclave) -&gt; Culexus/Callidus/character-snipes throttle it, screen the Librarians; (3) reserve-heavy -&gt; a whiffed turn-2 arrival (failed charges / scattered homers) is a lost tempo swing.</t>
         </is>
@@ -1734,10 +1758,10 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A17:B17"/>
     <mergeCell ref="A18:B18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
